--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_o_higgins.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_o_higgins.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>26.90791186718082</v>
+      </c>
+      <c r="C2">
         <v>29.69461011022802</v>
-      </c>
-      <c r="C2">
-        <v>26.90791186718082</v>
       </c>
       <c r="D2">
         <v>3.367614514175957</v>
       </c>
       <c r="E2">
-        <v>18.96177005023693</v>
+        <v>17.18229791411821</v>
       </c>
       <c r="F2">
         <v>63.85593203564487</v>
       </c>
       <c r="G2">
-        <v>17.18229791411821</v>
+        <v>18.96177005023693</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>26.60158633312995</v>
+      </c>
+      <c r="C3">
         <v>33.21537522879805</v>
-      </c>
-      <c r="C3">
-        <v>26.60158633312995</v>
       </c>
       <c r="D3">
         <v>3.010653930933137</v>
       </c>
       <c r="E3">
-        <v>20.78338550813164</v>
+        <v>16.64503321371306</v>
       </c>
       <c r="F3">
         <v>62.57158127815531</v>
       </c>
       <c r="G3">
-        <v>16.64503321371306</v>
+        <v>20.78338550813164</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>27.6661514683153</v>
+      </c>
+      <c r="C4">
         <v>40.00883197173769</v>
-      </c>
-      <c r="C4">
-        <v>27.6661514683153</v>
       </c>
       <c r="D4">
         <v>2.499448123620309</v>
       </c>
       <c r="E4">
-        <v>23.86094284961812</v>
+        <v>16.49986831709244</v>
       </c>
       <c r="F4">
         <v>59.63918883328945</v>
       </c>
       <c r="G4">
-        <v>16.49986831709244</v>
+        <v>23.86094284961812</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>28.55170297637312</v>
+      </c>
+      <c r="C5">
         <v>35.0644369438478</v>
-      </c>
-      <c r="C5">
-        <v>28.55170297637312</v>
       </c>
       <c r="D5">
         <v>2.85189236490921</v>
       </c>
       <c r="E5">
-        <v>21.43091565474237</v>
+        <v>17.4504196164846</v>
       </c>
       <c r="F5">
         <v>61.11866472877303</v>
       </c>
       <c r="G5">
-        <v>17.4504196164846</v>
+        <v>21.43091565474237</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.23076923076923</v>
+      </c>
+      <c r="C6">
         <v>32.38026124818578</v>
-      </c>
-      <c r="C6">
-        <v>29.23076923076923</v>
       </c>
       <c r="D6">
         <v>3.088301210219632</v>
       </c>
       <c r="E6">
-        <v>20.03592276605299</v>
+        <v>18.08711270767849</v>
       </c>
       <c r="F6">
         <v>61.87696452626852</v>
       </c>
       <c r="G6">
-        <v>18.08711270767849</v>
+        <v>20.03592276605299</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>30.45746929962665</v>
+      </c>
+      <c r="C7">
         <v>27.32670595114929</v>
-      </c>
-      <c r="C7">
-        <v>30.45746929962665</v>
       </c>
       <c r="D7">
         <v>3.659423868312757</v>
       </c>
       <c r="E7">
-        <v>17.31904096701542</v>
+        <v>19.30324714200188</v>
       </c>
       <c r="F7">
         <v>63.3777118909827</v>
       </c>
       <c r="G7">
-        <v>19.30324714200188</v>
+        <v>17.31904096701542</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>27.53136066262529</v>
+      </c>
+      <c r="C8">
         <v>33.89352379809135</v>
-      </c>
-      <c r="C8">
-        <v>27.53136066262529</v>
       </c>
       <c r="D8">
         <v>2.950416150168231</v>
       </c>
       <c r="E8">
-        <v>20.996467744934</v>
+        <v>17.05521472392638</v>
       </c>
       <c r="F8">
         <v>61.94831753113962</v>
       </c>
       <c r="G8">
-        <v>17.05521472392638</v>
+        <v>20.996467744934</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>32.83617424242424</v>
+      </c>
+      <c r="C9">
         <v>23.90506628787879</v>
-      </c>
-      <c r="C9">
-        <v>32.83617424242424</v>
       </c>
       <c r="D9">
         <v>4.183213666749196</v>
       </c>
       <c r="E9">
-        <v>15.2512932824831</v>
+        <v>20.94928822263338</v>
       </c>
       <c r="F9">
         <v>63.79941849488351</v>
       </c>
       <c r="G9">
-        <v>20.94928822263338</v>
+        <v>15.2512932824831</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>25.96523970605389</v>
+      </c>
+      <c r="C10">
         <v>37.69975504490844</v>
-      </c>
-      <c r="C10">
-        <v>25.96523970605389</v>
       </c>
       <c r="D10">
         <v>2.652537128712871</v>
       </c>
       <c r="E10">
-        <v>23.03470885895517</v>
+        <v>15.86487064357494</v>
       </c>
       <c r="F10">
         <v>61.10042049746988</v>
       </c>
       <c r="G10">
-        <v>15.86487064357494</v>
+        <v>23.03470885895517</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>29.8091864006464</v>
+      </c>
+      <c r="C11">
         <v>31.91000062154267</v>
-      </c>
-      <c r="C11">
-        <v>29.8091864006464</v>
       </c>
       <c r="D11">
         <v>3.133813790416829</v>
       </c>
       <c r="E11">
-        <v>19.73173450171029</v>
+        <v>18.43268380798647</v>
       </c>
       <c r="F11">
         <v>61.83558169030324</v>
       </c>
       <c r="G11">
-        <v>18.43268380798647</v>
+        <v>19.73173450171029</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>28.99381159752464</v>
+      </c>
+      <c r="C12">
         <v>31.68691267476507</v>
-      </c>
-      <c r="C12">
-        <v>28.99381159752464</v>
       </c>
       <c r="D12">
         <v>3.155877034358047</v>
       </c>
       <c r="E12">
-        <v>19.72041937094359</v>
+        <v>18.04436202838599</v>
       </c>
       <c r="F12">
         <v>62.23521860067043</v>
       </c>
       <c r="G12">
-        <v>18.04436202838599</v>
+        <v>19.72041937094359</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>26.82489923869234</v>
+      </c>
+      <c r="C13">
         <v>35.99417823555754</v>
-      </c>
-      <c r="C13">
-        <v>26.82489923869234</v>
       </c>
       <c r="D13">
         <v>2.778227060653188</v>
       </c>
       <c r="E13">
-        <v>22.10685553187101</v>
+        <v>16.47528020353435</v>
       </c>
       <c r="F13">
         <v>61.41786426459466</v>
       </c>
       <c r="G13">
-        <v>16.47528020353435</v>
+        <v>22.10685553187101</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>25.84151188255333</v>
+      </c>
+      <c r="C14">
         <v>37.05085570605888</v>
-      </c>
-      <c r="C14">
-        <v>25.84151188255333</v>
       </c>
       <c r="D14">
         <v>2.698992994746059</v>
       </c>
       <c r="E14">
-        <v>22.74560573619479</v>
+        <v>15.86416372055968</v>
       </c>
       <c r="F14">
         <v>61.39023054324553</v>
       </c>
       <c r="G14">
-        <v>15.86416372055968</v>
+        <v>22.74560573619479</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>25.29076396807298</v>
+      </c>
+      <c r="C15">
         <v>34.51539338654504</v>
-      </c>
-      <c r="C15">
-        <v>25.29076396807298</v>
       </c>
       <c r="D15">
         <v>2.897258011232243</v>
       </c>
       <c r="E15">
-        <v>21.59828754905459</v>
+        <v>15.82590082054941</v>
       </c>
       <c r="F15">
         <v>62.575811630396</v>
       </c>
       <c r="G15">
-        <v>15.82590082054941</v>
+        <v>21.59828754905459</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>28.51635305231445</v>
+      </c>
+      <c r="C16">
         <v>30.74527025301913</v>
-      </c>
-      <c r="C16">
-        <v>28.51635305231445</v>
       </c>
       <c r="D16">
         <v>3.252532801860156</v>
       </c>
       <c r="E16">
-        <v>19.30488313187342</v>
+        <v>17.90535124563147</v>
       </c>
       <c r="F16">
         <v>62.7897656224951</v>
       </c>
       <c r="G16">
-        <v>17.90535124563147</v>
+        <v>19.30488313187342</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>27.98491379310345</v>
+      </c>
+      <c r="C17">
         <v>27.79633620689655</v>
-      </c>
-      <c r="C17">
-        <v>27.98491379310345</v>
       </c>
       <c r="D17">
         <v>3.597596433417329</v>
       </c>
       <c r="E17">
-        <v>17.84318472659357</v>
+        <v>17.96423754020683</v>
       </c>
       <c r="F17">
         <v>64.1925777331996</v>
       </c>
       <c r="G17">
-        <v>17.96423754020683</v>
+        <v>17.84318472659357</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>27.01550520851239</v>
+      </c>
+      <c r="C18">
         <v>36.77931722075154</v>
-      </c>
-      <c r="C18">
-        <v>27.01550520851239</v>
       </c>
       <c r="D18">
         <v>2.718919424191438</v>
       </c>
       <c r="E18">
+        <v>16.49350376760489</v>
+      </c>
+      <c r="F18">
+        <v>61.05199084860315</v>
+      </c>
+      <c r="G18">
         <v>22.45450538379195</v>
-      </c>
-      <c r="F18">
-        <v>61.05199084860316</v>
-      </c>
-      <c r="G18">
-        <v>16.4935037676049</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>25.97324964507211</v>
+      </c>
+      <c r="C19">
         <v>32.08548158111036</v>
-      </c>
-      <c r="C19">
-        <v>25.97324964507211</v>
       </c>
       <c r="D19">
         <v>3.116674429436423</v>
       </c>
       <c r="E19">
+        <v>16.43265730629225</v>
+      </c>
+      <c r="F19">
+        <v>63.26762161395547</v>
+      </c>
+      <c r="G19">
         <v>20.29972107975228</v>
-      </c>
-      <c r="F19">
-        <v>63.26762161395546</v>
-      </c>
-      <c r="G19">
-        <v>16.43265730629225</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>27.38609112709832</v>
+      </c>
+      <c r="C20">
         <v>48.63309352517985</v>
-      </c>
-      <c r="C20">
-        <v>27.38609112709832</v>
       </c>
       <c r="D20">
         <v>2.056213017751479</v>
       </c>
       <c r="E20">
-        <v>27.62942779291553</v>
+        <v>15.55858310626703</v>
       </c>
       <c r="F20">
         <v>56.81198910081744</v>
       </c>
       <c r="G20">
-        <v>15.55858310626703</v>
+        <v>27.62942779291553</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>28.05400771538791</v>
+      </c>
+      <c r="C21">
         <v>38.91984569224175</v>
-      </c>
-      <c r="C21">
-        <v>28.05400771538791</v>
       </c>
       <c r="D21">
         <v>2.569383259911894</v>
       </c>
       <c r="E21">
-        <v>23.30894621999743</v>
+        <v>16.80143755615454</v>
       </c>
       <c r="F21">
         <v>59.88961622384803</v>
       </c>
       <c r="G21">
-        <v>16.80143755615454</v>
+        <v>23.30894621999743</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>23.43531293741252</v>
+      </c>
+      <c r="C22">
         <v>39.35212957408518</v>
-      </c>
-      <c r="C22">
-        <v>23.43531293741252</v>
       </c>
       <c r="D22">
         <v>2.541158536585366</v>
       </c>
       <c r="E22">
+        <v>14.39626581501044</v>
+      </c>
+      <c r="F22">
+        <v>61.42979977889694</v>
+      </c>
+      <c r="G22">
         <v>24.17393440609262</v>
-      </c>
-      <c r="F22">
-        <v>61.42979977889695</v>
-      </c>
-      <c r="G22">
-        <v>14.39626581501044</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>29.67200610221205</v>
+      </c>
+      <c r="C23">
         <v>53.49605898804983</v>
-      </c>
-      <c r="C23">
-        <v>29.67200610221205</v>
       </c>
       <c r="D23">
         <v>1.869296577946768</v>
       </c>
       <c r="E23">
+        <v>16.19933370349806</v>
+      </c>
+      <c r="F23">
+        <v>54.59466962798446</v>
+      </c>
+      <c r="G23">
         <v>29.20599666851749</v>
-      </c>
-      <c r="F23">
-        <v>54.59466962798444</v>
-      </c>
-      <c r="G23">
-        <v>16.19933370349806</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>23.32391471872592</v>
+      </c>
+      <c r="C24">
         <v>48.31749293603905</v>
-      </c>
-      <c r="C24">
-        <v>23.32391471872592</v>
       </c>
       <c r="D24">
         <v>2.069643806485912</v>
       </c>
       <c r="E24">
-        <v>28.15025441484585</v>
+        <v>13.58874588446573</v>
       </c>
       <c r="F24">
         <v>58.26099970068842</v>
       </c>
       <c r="G24">
-        <v>13.58874588446573</v>
+        <v>28.15025441484585</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>27.13538756286422</v>
+      </c>
+      <c r="C25">
         <v>31.278438572683</v>
-      </c>
-      <c r="C25">
-        <v>27.13538756286422</v>
       </c>
       <c r="D25">
         <v>3.197090537867671</v>
       </c>
       <c r="E25">
-        <v>19.7447655521681</v>
+        <v>17.12943132857971</v>
       </c>
       <c r="F25">
         <v>63.12580311925218</v>
       </c>
       <c r="G25">
-        <v>17.12943132857971</v>
+        <v>19.7447655521681</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>28.20132389865327</v>
+      </c>
+      <c r="C26">
         <v>40.73270942707145</v>
-      </c>
-      <c r="C26">
-        <v>28.20132389865327</v>
       </c>
       <c r="D26">
         <v>2.455029420005604</v>
       </c>
       <c r="E26">
-        <v>24.1116065396568</v>
+        <v>16.69369004188623</v>
       </c>
       <c r="F26">
         <v>59.19470341845696</v>
       </c>
       <c r="G26">
-        <v>16.69369004188623</v>
+        <v>24.1116065396568</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>27.4041133963313</v>
+      </c>
+      <c r="C27">
         <v>32.3256510026938</v>
-      </c>
-      <c r="C27">
-        <v>27.4041133963313</v>
       </c>
       <c r="D27">
         <v>3.093518518518518</v>
       </c>
       <c r="E27">
-        <v>20.23771281721812</v>
+        <v>17.15654781025806</v>
       </c>
       <c r="F27">
         <v>62.60573937252382</v>
       </c>
       <c r="G27">
-        <v>17.15654781025806</v>
+        <v>20.23771281721812</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>25.6198347107438</v>
+      </c>
+      <c r="C28">
         <v>43.65997638724912</v>
-      </c>
-      <c r="C28">
-        <v>25.6198347107438</v>
       </c>
       <c r="D28">
         <v>2.290427257977285</v>
       </c>
       <c r="E28">
-        <v>25.79160273399359</v>
+        <v>15.13460733714604</v>
       </c>
       <c r="F28">
-        <v>59.07378992886038</v>
+        <v>59.07378992886036</v>
       </c>
       <c r="G28">
-        <v>15.13460733714605</v>
+        <v>25.79160273399358</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>27.20051132213294</v>
+      </c>
+      <c r="C29">
         <v>33.79291453615778</v>
-      </c>
-      <c r="C29">
-        <v>27.20051132213294</v>
       </c>
       <c r="D29">
         <v>2.959200216157795</v>
       </c>
       <c r="E29">
-        <v>20.99024500907441</v>
+        <v>16.89541742286751</v>
       </c>
       <c r="F29">
         <v>62.11433756805808</v>
       </c>
       <c r="G29">
-        <v>16.89541742286751</v>
+        <v>20.99024500907441</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>24.38079424380794</v>
+      </c>
+      <c r="C30">
         <v>37.89954337899543</v>
-      </c>
-      <c r="C30">
-        <v>24.38079424380794</v>
       </c>
       <c r="D30">
         <v>2.63855421686747</v>
       </c>
       <c r="E30">
-        <v>23.3543656207367</v>
+        <v>15.02387448840382</v>
       </c>
       <c r="F30">
         <v>61.62175989085949</v>
       </c>
       <c r="G30">
-        <v>15.02387448840382</v>
+        <v>23.3543656207367</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>23.88625592417062</v>
+      </c>
+      <c r="C31">
         <v>37.52200406228842</v>
-      </c>
-      <c r="C31">
-        <v>23.88625592417062</v>
       </c>
       <c r="D31">
         <v>2.665102850956333</v>
       </c>
       <c r="E31">
-        <v>23.24664429530201</v>
+        <v>14.7986577181208</v>
       </c>
       <c r="F31">
-        <v>61.95469798657717</v>
+        <v>61.95469798657719</v>
       </c>
       <c r="G31">
-        <v>14.7986577181208</v>
+        <v>23.24664429530202</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>24.92265383293228</v>
+      </c>
+      <c r="C32">
         <v>34.51357854932967</v>
-      </c>
-      <c r="C32">
-        <v>24.92265383293228</v>
       </c>
       <c r="D32">
         <v>2.897410358565737</v>
       </c>
       <c r="E32">
-        <v>21.64726175075463</v>
+        <v>15.63173781802501</v>
       </c>
       <c r="F32">
         <v>62.72100043122035</v>
       </c>
       <c r="G32">
-        <v>15.63173781802501</v>
+        <v>21.64726175075463</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>24.98810090433127</v>
+      </c>
+      <c r="C33">
         <v>52.07044264635887</v>
-      </c>
-      <c r="C33">
-        <v>24.98810090433127</v>
       </c>
       <c r="D33">
         <v>1.920475319926874</v>
       </c>
       <c r="E33">
+        <v>14.11290322580645</v>
+      </c>
+      <c r="F33">
+        <v>56.47849462365591</v>
+      </c>
+      <c r="G33">
         <v>29.40860215053763</v>
-      </c>
-      <c r="F33">
-        <v>56.47849462365592</v>
-      </c>
-      <c r="G33">
-        <v>14.11290322580645</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>25.81056536692816</v>
+      </c>
+      <c r="C34">
         <v>33.23028171735518</v>
-      </c>
-      <c r="C34">
-        <v>25.81056536692816</v>
       </c>
       <c r="D34">
         <v>3.009303407372951</v>
       </c>
       <c r="E34">
-        <v>20.89418053699429</v>
+        <v>16.22889077876321</v>
       </c>
       <c r="F34">
         <v>62.8769286842425</v>
       </c>
       <c r="G34">
-        <v>16.22889077876321</v>
+        <v>20.89418053699429</v>
       </c>
     </row>
   </sheetData>
